--- a/Result/profitability/2207.xlsx
+++ b/Result/profitability/2207.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4275</v>
+        <v>8.17</v>
       </c>
       <c r="N2" t="n">
-        <v>18.96625</v>
+        <v>19.1375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>6.62375</v>
+        <v>7.3325</v>
       </c>
       <c r="N3" t="n">
-        <v>17.8125</v>
+        <v>17.85</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.88</v>
       </c>
       <c r="M4" t="n">
-        <v>5.740000000000001</v>
+        <v>6.55125</v>
       </c>
       <c r="N4" t="n">
-        <v>16.825</v>
+        <v>17.31</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>4.91875</v>
+        <v>5.7025</v>
       </c>
       <c r="N5" t="n">
-        <v>16.10375</v>
+        <v>16.45625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4.14625</v>
+        <v>4.59625</v>
       </c>
       <c r="N6" t="n">
-        <v>14.94375</v>
+        <v>14.83625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>3.080000000000001</v>
+        <v>3.64875</v>
       </c>
       <c r="N7" t="n">
-        <v>13.535</v>
+        <v>13.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>2.145</v>
+        <v>2.85375</v>
       </c>
       <c r="N8" t="n">
-        <v>12.3375</v>
+        <v>12.615</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.327500000000001</v>
+        <v>1.3275</v>
       </c>
       <c r="N9" t="n">
         <v>11.05375</v>
@@ -9332,42 +9332,42 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>65974</v>
+        <v>68066</v>
       </c>
       <c r="D71" t="n">
-        <v>52538</v>
+        <v>55393</v>
       </c>
       <c r="E71" t="n">
-        <v>13437</v>
+        <v>12673</v>
       </c>
       <c r="F71" t="n">
-        <v>20.37</v>
+        <v>18.62</v>
       </c>
       <c r="G71" t="n">
-        <v>8397</v>
+        <v>8529</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>12.73%</t>
+          <t>12.53%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-1807</v>
+        <v>-2134</v>
       </c>
       <c r="J71" t="n">
-        <v>6590</v>
+        <v>6395</v>
       </c>
       <c r="K71" t="n">
-        <v>4290</v>
+        <v>4097</v>
       </c>
       <c r="L71" t="n">
-        <v>7.7</v>
+        <v>7.35</v>
       </c>
       <c r="M71" t="n">
-        <v>8.856249999999999</v>
+        <v>8.8125</v>
       </c>
       <c r="N71" t="n">
-        <v>19.975</v>
+        <v>19.75625</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9394,28 +9394,28 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>0.5700000000000003</v>
+        <v>0.2199999999999998</v>
       </c>
       <c r="X71" t="n">
-        <v>0.07994389901823284</v>
+        <v>0.03085553997194945</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.810000000000002</v>
+        <v>1.060000000000002</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.1600227790432802</v>
+        <v>0.06036446469248302</v>
       </c>
       <c r="AA71" t="n">
-        <v>-2.839999999999999</v>
+        <v>-3.19</v>
       </c>
       <c r="AB71" t="n">
-        <v>-0.2694497153700189</v>
+        <v>-0.3026565464895635</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.370000000000001</v>
+        <v>-0.379999999999999</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.07210526315789489</v>
+        <v>-0.01999999999999991</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -9427,14 +9427,14 @@
         <v>1</v>
       </c>
       <c r="AH71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率成長</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9459,42 +9459,42 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>70722</v>
+        <v>68630</v>
       </c>
       <c r="D72" t="n">
-        <v>54979</v>
+        <v>52124</v>
       </c>
       <c r="E72" t="n">
-        <v>15743</v>
+        <v>16506</v>
       </c>
       <c r="F72" t="n">
-        <v>22.26</v>
+        <v>24.05</v>
       </c>
       <c r="G72" t="n">
-        <v>10861</v>
+        <v>10728</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>15.63%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>-2995</v>
+        <v>-2668</v>
       </c>
       <c r="J72" t="n">
-        <v>7866</v>
+        <v>8060</v>
       </c>
       <c r="K72" t="n">
-        <v>5583</v>
+        <v>5776</v>
       </c>
       <c r="L72" t="n">
-        <v>10.02</v>
+        <v>10.37</v>
       </c>
       <c r="M72" t="n">
         <v>8.685</v>
       </c>
       <c r="N72" t="n">
-        <v>20.2325</v>
+        <v>20.2375</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -9521,28 +9521,28 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>2.319999999999999</v>
+        <v>3.02</v>
       </c>
       <c r="X72" t="n">
-        <v>0.3012987012987012</v>
+        <v>0.4108843537414966</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.890000000000001</v>
+        <v>5.43</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.09278350515463929</v>
+        <v>0.2916219119226637</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.3046875</v>
+        <v>0.3502604166666665</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.190000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.1091180866965622</v>
+        <v>0.1983059292476332</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9621,7 +9621,7 @@
         <v>8.831250000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>20.425</v>
+        <v>20.43</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -9648,16 +9648,16 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.9499999999999993</v>
+        <v>-1.299999999999999</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.09481037924151692</v>
+        <v>-0.1253616200578591</v>
       </c>
       <c r="Y73" t="n">
-        <v>-1.380000000000003</v>
+        <v>-3.170000000000002</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.06199460916442057</v>
+        <v>-0.1318087318087319</v>
       </c>
       <c r="AA73" t="n">
         <v>1.12</v>
@@ -9745,10 +9745,10 @@
         <v>7.95</v>
       </c>
       <c r="M74" t="n">
-        <v>8.505000000000001</v>
+        <v>8.504999999999999</v>
       </c>
       <c r="N74" t="n">
-        <v>20.0575</v>
+        <v>20.0625</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>87606</v>
+      </c>
+      <c r="D75" t="n">
+        <v>68856</v>
+      </c>
+      <c r="E75" t="n">
+        <v>18750</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11664</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-978</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10686</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7585</v>
+      </c>
+      <c r="L75" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.3625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>5.669999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7132075471698112</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.219999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1157455683003128</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8530612244897959</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.779999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1493018259935552</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
